--- a/ZlaataQA/src/test/resources/ImportFile/RawMaterial.xlsx
+++ b/ZlaataQA/src/test/resources/ImportFile/RawMaterial.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Material-type</t>
   </si>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>Auto Material 741</t>
+  </si>
+  <si>
+    <t>Test211</t>
+  </si>
+  <si>
+    <t>Auto Material 351</t>
+  </si>
+  <si>
+    <t>Test133</t>
+  </si>
+  <si>
+    <t>Auto Material 573</t>
   </si>
 </sst>
 </file>
@@ -666,10 +678,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>14</v>
